--- a/stock_tracker.xlsx
+++ b/stock_tracker.xlsx
@@ -1,76 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Side_projects\stocks-tracker\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098A26D7-DD36-477D-9043-DE588F9B28A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
-  <si>
-    <t>stock</t>
-  </si>
-  <si>
-    <t>Buy Price</t>
-  </si>
-  <si>
-    <t>Current Price</t>
-  </si>
-  <si>
-    <t>P/L</t>
-  </si>
-  <si>
-    <t>AAPL</t>
-  </si>
-  <si>
-    <t>GOOGL</t>
-  </si>
-  <si>
-    <t>TSLA</t>
-  </si>
-  <si>
-    <t>AMZN</t>
-  </si>
-  <si>
-    <t>MSFT</t>
-  </si>
-  <si>
-    <t>NKE</t>
-  </si>
-  <si>
-    <t>FB</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -89,21 +47,80 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -391,124 +408,145 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="11.453125" customWidth="1"/>
-    <col min="3" max="3" width="14.08984375" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Stock</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Buy Price</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>P/L</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>AAPL</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>100</v>
       </c>
-      <c r="C2">
-        <v>299.13</v>
-      </c>
-      <c r="D2">
-        <v>199.13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3">
+      <c r="C2" t="n">
+        <v>298.49</v>
+      </c>
+      <c r="D2" t="n">
+        <v>198.49</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3000</v>
       </c>
-      <c r="C3">
-        <v>346.8</v>
-      </c>
-      <c r="D3">
-        <v>-2653.2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4">
+      <c r="C3" t="n">
+        <v>346.2</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-2653.8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>TSLA</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>700</v>
       </c>
-      <c r="C4">
-        <v>381.89</v>
-      </c>
-      <c r="D4">
-        <v>-318.11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5">
+      <c r="C4" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="D4" t="n">
+        <v>-319.22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>AMZN</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
         <v>300</v>
       </c>
-      <c r="C5">
-        <v>235.24</v>
-      </c>
-      <c r="D5">
-        <v>-64.760000000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6">
+      <c r="C5" t="n">
+        <v>235.19</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-64.81</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MSFT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
         <v>250</v>
       </c>
-      <c r="C6">
-        <v>373.86</v>
-      </c>
-      <c r="D6">
-        <v>123.86</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7">
+      <c r="C6" t="n">
+        <v>373.61</v>
+      </c>
+      <c r="D6" t="n">
+        <v>123.61</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NKE</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
         <v>150</v>
       </c>
-      <c r="C7">
-        <v>42.78</v>
-      </c>
-      <c r="D7">
-        <v>-107.22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8">
+      <c r="C7" t="n">
+        <v>42.76</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-107.24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FB</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
         <v>350</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="n">
         <v>44.52</v>
       </c>
-      <c r="D8">
+      <c r="D8" t="n">
         <v>-305.48</v>
       </c>
     </row>

--- a/stock_tracker.xlsx
+++ b/stock_tracker.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,10 +448,10 @@
         <v>100</v>
       </c>
       <c r="C2" t="n">
-        <v>298.49</v>
+        <v>278.45</v>
       </c>
       <c r="D2" t="n">
-        <v>198.49</v>
+        <v>178.45</v>
       </c>
     </row>
     <row r="3">
@@ -464,10 +464,10 @@
         <v>3000</v>
       </c>
       <c r="C3" t="n">
-        <v>346.2</v>
+        <v>343.06</v>
       </c>
       <c r="D3" t="n">
-        <v>-2653.8</v>
+        <v>-2656.94</v>
       </c>
     </row>
     <row r="4">
@@ -480,10 +480,10 @@
         <v>700</v>
       </c>
       <c r="C4" t="n">
-        <v>380.78</v>
+        <v>386.76</v>
       </c>
       <c r="D4" t="n">
-        <v>-319.22</v>
+        <v>-313.24</v>
       </c>
     </row>
     <row r="5">
@@ -496,10 +496,10 @@
         <v>300</v>
       </c>
       <c r="C5" t="n">
-        <v>235.19</v>
+        <v>232.32</v>
       </c>
       <c r="D5" t="n">
-        <v>-64.81</v>
+        <v>-67.68000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -512,10 +512,10 @@
         <v>250</v>
       </c>
       <c r="C6" t="n">
-        <v>373.61</v>
+        <v>371.09</v>
       </c>
       <c r="D6" t="n">
-        <v>123.61</v>
+        <v>121.09</v>
       </c>
     </row>
     <row r="7">
@@ -528,26 +528,10 @@
         <v>150</v>
       </c>
       <c r="C7" t="n">
-        <v>42.76</v>
+        <v>41.19</v>
       </c>
       <c r="D7" t="n">
-        <v>-107.24</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>FB</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>350</v>
-      </c>
-      <c r="C8" t="n">
-        <v>44.52</v>
-      </c>
-      <c r="D8" t="n">
-        <v>-305.48</v>
+        <v>-108.81</v>
       </c>
     </row>
   </sheetData>
